--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DFS_HRM-2031-0212/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Front_Summary.xlsx
@@ -419,32 +419,22 @@
     <row r="1">
       <c r="C1" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Distance 1</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
+          <t>Distance 2</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Mean Stepheight</t>
+          <t>Angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Area</t>
         </is>
       </c>
     </row>
@@ -456,26 +446,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Fiducial 1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.38869</v>
+        <v>124.76048</v>
       </c>
       <c r="D2" t="n">
-        <v>17.04626</v>
+        <v>87.71243</v>
       </c>
       <c r="E2" t="n">
-        <v>17.14952</v>
+        <v>92.5586</v>
       </c>
       <c r="F2" t="n">
-        <v>43.28744</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.05203</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.85108</v>
+        <v>521.35198</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +469,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.2207</v>
+        <v>123.46303</v>
       </c>
       <c r="D3" t="n">
-        <v>17.10524</v>
+        <v>88.867</v>
       </c>
       <c r="E3" t="n">
-        <v>16.86082</v>
+        <v>92.14606999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>43.54548</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.05129</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.8535</v>
+        <v>520.4373399999999</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +488,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.32359</v>
+        <v>124.50956</v>
       </c>
       <c r="D4" t="n">
-        <v>16.989</v>
+        <v>88.21684999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>17.07718</v>
+        <v>93.11107</v>
       </c>
       <c r="F4" t="n">
-        <v>42.76686</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.05125</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.86044</v>
+        <v>529.61078</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +507,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.34711</v>
+        <v>122.25446</v>
       </c>
       <c r="D5" t="n">
-        <v>16.59279</v>
+        <v>87.25801</v>
       </c>
       <c r="E5" t="n">
-        <v>17.05231</v>
+        <v>91.45863</v>
       </c>
       <c r="F5" t="n">
-        <v>44.09847</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.05165</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1.8725</v>
+        <v>525.22419</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +526,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.35477</v>
+        <v>124.13142</v>
       </c>
       <c r="D6" t="n">
-        <v>17.10962</v>
+        <v>87.40007</v>
       </c>
       <c r="E6" t="n">
-        <v>17.01649</v>
+        <v>92.05515</v>
       </c>
       <c r="F6" t="n">
-        <v>42.64502</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.05099</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.88894</v>
+        <v>532.07235</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +545,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.87122</v>
+        <v>123.36017</v>
       </c>
       <c r="D7" t="n">
-        <v>16.77966</v>
+        <v>86.50033000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>16.97879</v>
+        <v>92.79514</v>
       </c>
       <c r="F7" t="n">
-        <v>43.94901</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.05046</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1.87903</v>
+        <v>524.89755</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +564,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.87045</v>
+        <v>121.86482</v>
       </c>
       <c r="D8" t="n">
-        <v>16.6659</v>
+        <v>88.18707999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>16.98921</v>
+        <v>91.89239999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>43.81255</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.05112</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1.88228</v>
+        <v>536.71925</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +583,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.4302</v>
+        <v>123.32463</v>
       </c>
       <c r="D9" t="n">
-        <v>16.58128</v>
+        <v>86.47704</v>
       </c>
       <c r="E9" t="n">
-        <v>16.69495</v>
+        <v>92.94052000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>42.11305</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.05119</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.84739</v>
+        <v>516.1409200000001</v>
       </c>
     </row>
     <row r="10">
@@ -660,53 +602,27 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.04898</v>
+        <v>124.62905</v>
       </c>
       <c r="D10" t="n">
-        <v>16.66213</v>
+        <v>88.06827</v>
       </c>
       <c r="E10" t="n">
-        <v>17.05854</v>
+        <v>93.49162</v>
       </c>
       <c r="F10" t="n">
-        <v>43.82238</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.05153</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.84423</v>
+        <v>517.16907</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Height</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Radius</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bump</t>
+          <t>Diameter</t>
         </is>
       </c>
     </row>
@@ -718,26 +634,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Micro Bump 3</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.90768</v>
+        <v>8.6776</v>
       </c>
       <c r="D12" t="n">
-        <v>17.05083</v>
-      </c>
-      <c r="E12" t="n">
-        <v>16.92633</v>
-      </c>
-      <c r="F12" t="n">
-        <v>43.38592</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.05264</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1.84575</v>
+        <v>24.36972</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +651,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.00884</v>
+        <v>8.921580000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>17.23181</v>
-      </c>
-      <c r="E13" t="n">
-        <v>16.94379</v>
-      </c>
-      <c r="F13" t="n">
-        <v>43.05328</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.05273</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.88532</v>
+        <v>24.57278</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +664,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.99395</v>
+        <v>8.6686</v>
       </c>
       <c r="D14" t="n">
-        <v>16.7628</v>
-      </c>
-      <c r="E14" t="n">
-        <v>17.06532</v>
-      </c>
-      <c r="F14" t="n">
-        <v>43.55069</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.05162</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1.85775</v>
+        <v>24.96078</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +677,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.09115</v>
+        <v>8.798719999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>16.9807</v>
-      </c>
-      <c r="E15" t="n">
-        <v>16.91954</v>
-      </c>
-      <c r="F15" t="n">
-        <v>42.91243</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.05019</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.85199</v>
+        <v>25.07931</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +690,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.11991</v>
+        <v>8.78797</v>
       </c>
       <c r="D16" t="n">
-        <v>17.05103</v>
-      </c>
-      <c r="E16" t="n">
-        <v>16.79468</v>
-      </c>
-      <c r="F16" t="n">
-        <v>42.9911</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.05011</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.91096</v>
+        <v>25.17339</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +703,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.15659</v>
+        <v>8.57203</v>
       </c>
       <c r="D17" t="n">
-        <v>17.14665</v>
-      </c>
-      <c r="E17" t="n">
-        <v>17.09554</v>
-      </c>
-      <c r="F17" t="n">
-        <v>42.99613</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.05122</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.81571</v>
+        <v>24.97678</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +716,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.11789</v>
+        <v>8.73115</v>
       </c>
       <c r="D18" t="n">
-        <v>17.25399</v>
-      </c>
-      <c r="E18" t="n">
-        <v>17.06258</v>
-      </c>
-      <c r="F18" t="n">
-        <v>42.73864</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.05124</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1.83716</v>
+        <v>24.24121</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +729,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.76423</v>
+        <v>8.80228</v>
       </c>
       <c r="D19" t="n">
-        <v>16.60283</v>
-      </c>
-      <c r="E19" t="n">
-        <v>16.89313</v>
-      </c>
-      <c r="F19" t="n">
-        <v>43.43386</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.05236</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.88732</v>
+        <v>24.93208</v>
       </c>
     </row>
     <row r="20">
@@ -922,31 +742,39 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.84976</v>
+        <v>8.743220000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>17.04064</v>
-      </c>
-      <c r="E20" t="n">
-        <v>16.93555</v>
-      </c>
-      <c r="F20" t="n">
-        <v>42.91067</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.05058</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.82165</v>
+        <v>25.25401</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
@@ -960,14 +788,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.6173999999999999</v>
+        <v>17.5947</v>
       </c>
       <c r="D22" t="n">
-        <v>1.13522</v>
+        <v>16.98479</v>
+      </c>
+      <c r="E22" t="n">
+        <v>17.03038</v>
+      </c>
+      <c r="F22" t="n">
+        <v>43.45864</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.05032</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.87383</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +817,22 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.60987</v>
+        <v>17.38349</v>
       </c>
       <c r="D23" t="n">
-        <v>1.13786</v>
+        <v>16.73294</v>
+      </c>
+      <c r="E23" t="n">
+        <v>17.04231</v>
+      </c>
+      <c r="F23" t="n">
+        <v>43.60506</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.85752</v>
       </c>
     </row>
     <row r="24">
@@ -990,10 +842,22 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.609</v>
+        <v>17.12778</v>
       </c>
       <c r="D24" t="n">
-        <v>1.1299</v>
+        <v>17.04326</v>
+      </c>
+      <c r="E24" t="n">
+        <v>17.11708</v>
+      </c>
+      <c r="F24" t="n">
+        <v>43.34785</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.05172</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.90775</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +867,22 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.61303</v>
+        <v>17.2908</v>
       </c>
       <c r="D25" t="n">
-        <v>1.13008</v>
+        <v>16.64991</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.18919</v>
+      </c>
+      <c r="F25" t="n">
+        <v>43.07293</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.05102</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.79953</v>
       </c>
     </row>
     <row r="26">
@@ -1016,10 +892,22 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.63282</v>
+        <v>17.36096</v>
       </c>
       <c r="D26" t="n">
-        <v>1.14125</v>
+        <v>16.85789</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.95003</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42.91668</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.05144</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.85938</v>
       </c>
     </row>
     <row r="27">
@@ -1029,10 +917,22 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.62056</v>
+        <v>17.13817</v>
       </c>
       <c r="D27" t="n">
-        <v>1.15128</v>
+        <v>16.73503</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.9998</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42.68463</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.05039</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.88026</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +942,22 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.6133999999999999</v>
+        <v>16.84973</v>
       </c>
       <c r="D28" t="n">
-        <v>1.16359</v>
+        <v>16.70244</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.73339</v>
+      </c>
+      <c r="F28" t="n">
+        <v>43.8129</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.85153</v>
       </c>
     </row>
     <row r="29">
@@ -1055,10 +967,22 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.61611</v>
+        <v>17.12472</v>
       </c>
       <c r="D29" t="n">
-        <v>1.13383</v>
+        <v>16.75598</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.85298</v>
+      </c>
+      <c r="F29" t="n">
+        <v>43.5392</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.05173</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.87373</v>
       </c>
     </row>
     <row r="30">
@@ -1068,10 +992,22 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.62307</v>
+        <v>17.37257</v>
       </c>
       <c r="D30" t="n">
-        <v>1.15242</v>
+        <v>16.61201</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.91063</v>
+      </c>
+      <c r="F30" t="n">
+        <v>43.97214</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.05197</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.83579</v>
       </c>
     </row>
     <row r="31">
@@ -1128,28 +1064,28 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.75946</v>
+        <v>0.7762</v>
       </c>
       <c r="D32" t="n">
-        <v>0.08345</v>
+        <v>0.08303000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>0.61546</v>
+        <v>0.62198</v>
       </c>
       <c r="F32" t="n">
-        <v>0.98791</v>
+        <v>0.97357</v>
       </c>
       <c r="G32" t="n">
-        <v>0.10934</v>
+        <v>0.11317</v>
       </c>
       <c r="H32" t="n">
-        <v>0.007889999999999999</v>
+        <v>0.00779</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09540999999999999</v>
+        <v>0.09536</v>
       </c>
       <c r="J32" t="n">
-        <v>0.12779</v>
+        <v>0.12998</v>
       </c>
     </row>
     <row r="33">
@@ -1159,28 +1095,28 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7755300000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08235000000000001</v>
+        <v>0.08026999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.6158</v>
+        <v>0.6362100000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>0.96332</v>
+        <v>0.9658600000000001</v>
       </c>
       <c r="G33" t="n">
-        <v>0.10957</v>
+        <v>0.11214</v>
       </c>
       <c r="H33" t="n">
-        <v>0.00775</v>
+        <v>0.00771</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09649000000000001</v>
+        <v>0.09311</v>
       </c>
       <c r="J33" t="n">
-        <v>0.13049</v>
+        <v>0.12719</v>
       </c>
     </row>
     <row r="34">
@@ -1190,28 +1126,28 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.75327</v>
+        <v>0.7719200000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08074000000000001</v>
+        <v>0.08162</v>
       </c>
       <c r="E34" t="n">
-        <v>0.61065</v>
+        <v>0.60723</v>
       </c>
       <c r="F34" t="n">
-        <v>0.96651</v>
+        <v>0.97031</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11166</v>
+        <v>0.11199</v>
       </c>
       <c r="H34" t="n">
-        <v>0.00784</v>
+        <v>0.0077</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09569</v>
+        <v>0.0963</v>
       </c>
       <c r="J34" t="n">
-        <v>0.13106</v>
+        <v>0.12895</v>
       </c>
     </row>
     <row r="35">
@@ -1221,28 +1157,28 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.76963</v>
+        <v>0.76212</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0832</v>
+        <v>0.08277</v>
       </c>
       <c r="E35" t="n">
-        <v>0.60971</v>
+        <v>0.61613</v>
       </c>
       <c r="F35" t="n">
-        <v>0.97001</v>
+        <v>0.9779600000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>0.11029</v>
+        <v>0.11181</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00775</v>
+        <v>0.00772</v>
       </c>
       <c r="I35" t="n">
-        <v>0.09432</v>
+        <v>0.09499</v>
       </c>
       <c r="J35" t="n">
-        <v>0.12962</v>
+        <v>0.13115</v>
       </c>
     </row>
     <row r="36">
@@ -1252,28 +1188,28 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.767</v>
+        <v>0.7475000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08283</v>
+        <v>0.08278000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.61393</v>
+        <v>0.60629</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9819</v>
+        <v>0.9937</v>
       </c>
       <c r="G36" t="n">
-        <v>0.11114</v>
+        <v>0.11219</v>
       </c>
       <c r="H36" t="n">
-        <v>0.00773</v>
+        <v>0.00763</v>
       </c>
       <c r="I36" t="n">
-        <v>0.09524000000000001</v>
+        <v>0.09586</v>
       </c>
       <c r="J36" t="n">
-        <v>0.12975</v>
+        <v>0.12673</v>
       </c>
     </row>
     <row r="37">
@@ -1283,28 +1219,28 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.75987</v>
+        <v>0.75015</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0823</v>
+        <v>0.08161</v>
       </c>
       <c r="E37" t="n">
-        <v>0.62369</v>
+        <v>0.61507</v>
       </c>
       <c r="F37" t="n">
-        <v>0.96206</v>
+        <v>0.97623</v>
       </c>
       <c r="G37" t="n">
-        <v>0.11036</v>
+        <v>0.10943</v>
       </c>
       <c r="H37" t="n">
-        <v>0.00773</v>
+        <v>0.0077</v>
       </c>
       <c r="I37" t="n">
-        <v>0.09377000000000001</v>
+        <v>0.09363</v>
       </c>
       <c r="J37" t="n">
-        <v>0.12914</v>
+        <v>0.12948</v>
       </c>
     </row>
     <row r="38">
@@ -1314,28 +1250,28 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.76905</v>
+        <v>0.76791</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08282</v>
+        <v>0.08237</v>
       </c>
       <c r="E38" t="n">
-        <v>0.6274</v>
+        <v>0.61202</v>
       </c>
       <c r="F38" t="n">
-        <v>0.96733</v>
+        <v>0.96774</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11292</v>
+        <v>0.11118</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00766</v>
+        <v>0.00777</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0953</v>
+        <v>0.09597</v>
       </c>
       <c r="J38" t="n">
-        <v>0.12808</v>
+        <v>0.12896</v>
       </c>
     </row>
     <row r="39">
@@ -1345,28 +1281,28 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.76048</v>
+        <v>0.76511</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08094999999999999</v>
+        <v>0.08155999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>0.61608</v>
+        <v>0.61682</v>
       </c>
       <c r="F39" t="n">
-        <v>0.97739</v>
+        <v>0.97407</v>
       </c>
       <c r="G39" t="n">
-        <v>0.11177</v>
+        <v>0.11067</v>
       </c>
       <c r="H39" t="n">
-        <v>0.00777</v>
+        <v>0.00769</v>
       </c>
       <c r="I39" t="n">
-        <v>0.09475</v>
+        <v>0.09351</v>
       </c>
       <c r="J39" t="n">
-        <v>0.1293</v>
+        <v>0.12882</v>
       </c>
     </row>
     <row r="40">
@@ -1376,28 +1312,28 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.7592</v>
+        <v>0.76225</v>
       </c>
       <c r="D40" t="n">
-        <v>0.08108</v>
+        <v>0.08278000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>0.62524</v>
+        <v>0.61268</v>
       </c>
       <c r="F40" t="n">
-        <v>1.00371</v>
+        <v>0.96916</v>
       </c>
       <c r="G40" t="n">
-        <v>0.11162</v>
+        <v>0.11173</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00781</v>
+        <v>0.00751</v>
       </c>
       <c r="I40" t="n">
-        <v>0.09578</v>
+        <v>0.09496</v>
       </c>
       <c r="J40" t="n">
-        <v>0.12826</v>
+        <v>0.1277</v>
       </c>
     </row>
   </sheetData>
